--- a/DRL-Experiment-Analyzer/results/report.xlsx
+++ b/DRL-Experiment-Analyzer/results/report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,7 +740,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CartPole-v1</t>
+          <t>Acrobot-v1</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -748,101 +748,101 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>run-20260729_170249-3szo1zw5</t>
+          <t>run-20260806_111231-qnts3ypd</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="F3" t="n">
-        <v>500</v>
+        <v>-485.1</v>
       </c>
       <c r="G3" t="n">
-        <v>9.538461538461538</v>
+        <v>-500</v>
       </c>
       <c r="H3" t="n">
-        <v>420.4216783216783</v>
+        <v>-498.2142857142857</v>
       </c>
       <c r="I3" t="n">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="J3" t="n">
-        <v>178.6171124549762</v>
+        <v>3.842302137298117</v>
       </c>
       <c r="K3" t="n">
-        <v>31904.07286175362</v>
+        <v>14.76328571428568</v>
       </c>
       <c r="L3" t="n">
-        <v>4369.869230769231</v>
+        <v>-9962.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001817976735765114</v>
+        <v>4483.95068359375</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2499055561883441</v>
+        <v>4788.676675186157</v>
       </c>
       <c r="O3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1113</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>547.3053036</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-498.125</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-498.7420775286257</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.007712147659092994</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-499.8576654837446</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-496.5709059448268</v>
+      </c>
+      <c r="W3" t="n">
         <v>11</v>
       </c>
-      <c r="P3" t="n">
-        <v>2092</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>216.3186257</v>
-      </c>
-      <c r="R3" t="n">
-        <v>420.4216783216783</v>
-      </c>
-      <c r="S3" t="n">
-        <v>304.8273136231877</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.4248522891778916</v>
-      </c>
-      <c r="U3" t="n">
-        <v>314.8657102695192</v>
-      </c>
-      <c r="V3" t="n">
-        <v>525.9776463738374</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
       <c r="X3" t="n">
-        <v>475.4769230769231</v>
+        <v>-485.845</v>
       </c>
       <c r="Y3" t="n">
-        <v>420.4216783216783</v>
+        <v>-498.2142857142857</v>
       </c>
       <c r="Z3" t="n">
-        <v>178.6171124549762</v>
+        <v>3.842302137298117</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>-485.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>36.29006993006994</v>
+        <v>-0.02701298701299018</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4248522891778916</v>
+        <v>0.007712147659092994</v>
       </c>
       <c r="AF3" t="n">
-        <v>70.18271350618231</v>
+        <v>99.23468743757748</v>
       </c>
       <c r="AG3" t="n">
-        <v>397.2608391608392</v>
+        <v>-474.4047619047619</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pendulum-v1</t>
+          <t>CartPole-v1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -863,97 +863,99 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>run-20260729_144514-wf9cakkf</t>
+          <t>run-20260729_170249-3szo1zw5</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-1326.359434524682</v>
+        <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>-1162.450953943689</v>
+        <v>500</v>
       </c>
       <c r="G4" t="n">
-        <v>-1683.245237411418</v>
+        <v>9.538461538461538</v>
       </c>
       <c r="H4" t="n">
-        <v>-1344.243409150519</v>
+        <v>420.4216783216783</v>
       </c>
       <c r="I4" t="n">
-        <v>-1290.341343171411</v>
+        <v>500</v>
       </c>
       <c r="J4" t="n">
-        <v>163.1298229843652</v>
+        <v>178.6171124549762</v>
       </c>
       <c r="K4" t="n">
-        <v>26611.33914691033</v>
+        <v>31904.07286175362</v>
       </c>
       <c r="L4" t="n">
-        <v>-13542.27230642153</v>
+        <v>4369.869230769231</v>
       </c>
       <c r="M4" t="n">
-        <v>625.8033447265625</v>
+        <v>0.0001817976735765114</v>
       </c>
       <c r="N4" t="n">
-        <v>3027.25532455542</v>
+        <v>0.2499055561883441</v>
       </c>
       <c r="O4" t="n">
         <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>1011</v>
+        <v>2092</v>
       </c>
       <c r="Q4" t="n">
-        <v>168.8450533</v>
+        <v>216.3186257</v>
       </c>
       <c r="R4" t="n">
-        <v>-1344.243409150519</v>
+        <v>420.4216783216783</v>
       </c>
       <c r="S4" t="n">
-        <v>-1284.561832095834</v>
+        <v>304.8273136231877</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1213543781385942</v>
+        <v>0.4248522891778916</v>
       </c>
       <c r="U4" t="n">
-        <v>-1440.646973997267</v>
+        <v>314.8657102695192</v>
       </c>
       <c r="V4" t="n">
-        <v>-1247.839844303772</v>
+        <v>525.9776463738374</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-1188.490668117076</v>
+        <v>475.4769230769231</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1344.243409150519</v>
+        <v>420.4216783216783</v>
       </c>
       <c r="Z4" t="n">
-        <v>163.1298229843652</v>
+        <v>178.6171124549762</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1162.450953943689</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3.069093075021819</v>
+        <v>36.29006993006994</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1213543781385942</v>
+        <v>0.4248522891778916</v>
       </c>
       <c r="AF4" t="n">
-        <v>89.17787449672798</v>
+        <v>70.18271350618231</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1231.115664220139</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>397.2608391608392</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
       <c r="AI4" t="b">
         <v>0</v>
       </c>
@@ -963,7 +965,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DDPG</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,95 +978,97 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>run-20260729_143142-0xxw6y6p</t>
+          <t>run-20260729_144514-wf9cakkf</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-220.5741539286572</v>
+        <v>-1326.359434524682</v>
       </c>
       <c r="F5" t="n">
-        <v>-197.8141914628206</v>
+        <v>-1162.450953943689</v>
       </c>
       <c r="G5" t="n">
-        <v>-1162.450953943689</v>
+        <v>-1683.245237411418</v>
       </c>
       <c r="H5" t="n">
-        <v>-359.1719996496569</v>
+        <v>-1344.243409150519</v>
       </c>
       <c r="I5" t="n">
-        <v>-244.0348557501347</v>
+        <v>-1290.341343171411</v>
       </c>
       <c r="J5" t="n">
-        <v>285.9389227629062</v>
+        <v>163.1298229843652</v>
       </c>
       <c r="K5" t="n">
-        <v>81761.06755081125</v>
+        <v>26611.33914691033</v>
       </c>
       <c r="L5" t="n">
-        <v>-3259.379442210054</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>-13542.27230642153</v>
+      </c>
+      <c r="M5" t="n">
+        <v>625.8033447265625</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3027.25532455542</v>
+      </c>
       <c r="O5" t="n">
         <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>49901</v>
+        <v>1011</v>
       </c>
       <c r="Q5" t="n">
-        <v>782.6554901</v>
+        <v>168.8450533</v>
       </c>
       <c r="R5" t="n">
-        <v>-359.1719996496569</v>
+        <v>-1344.243409150519</v>
       </c>
       <c r="S5" t="n">
-        <v>-597.4437800681523</v>
+        <v>-1284.561832095834</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7961058296354292</v>
+        <v>0.1213543781385942</v>
       </c>
       <c r="U5" t="n">
-        <v>-528.1511046256048</v>
+        <v>-1440.646973997267</v>
       </c>
       <c r="V5" t="n">
-        <v>-190.1928946737091</v>
+        <v>-1247.839844303772</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-246.0460295868641</v>
+        <v>-1188.490668117076</v>
       </c>
       <c r="Y5" t="n">
-        <v>-359.1719996496569</v>
+        <v>-1344.243409150519</v>
       </c>
       <c r="Z5" t="n">
-        <v>285.9389227629062</v>
+        <v>163.1298229843652</v>
       </c>
       <c r="AA5" t="n">
-        <v>-197.8141914628206</v>
+        <v>-1162.450953943689</v>
       </c>
       <c r="AB5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>49.90377853411189</v>
+        <v>-3.069093075021819</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.7961058296354292</v>
+        <v>0.1213543781385942</v>
       </c>
       <c r="AF5" t="n">
-        <v>55.67600658603611</v>
+        <v>89.17787449672798</v>
       </c>
       <c r="AG5" t="n">
-        <v>-296.3072220190958</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1</v>
-      </c>
+        <v>-1231.115664220139</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
         <v>0</v>
       </c>
@@ -1074,12 +1078,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Acrobot-v1</t>
+          <t>Pendulum-v1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1087,99 +1091,101 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>run-20260729_154543-f2vuqnfe</t>
+          <t>run-20260806_152025-lrqwmvdy</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-500</v>
+        <v>-1229.122733557015</v>
       </c>
       <c r="F6" t="n">
-        <v>-500</v>
+        <v>-1109.937787599805</v>
       </c>
       <c r="G6" t="n">
-        <v>-500</v>
+        <v>-1533.468066104518</v>
       </c>
       <c r="H6" t="n">
-        <v>-500</v>
+        <v>-1253.427681164352</v>
       </c>
       <c r="I6" t="n">
-        <v>-500</v>
+        <v>-1229.122733557015</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>114.5046436055966</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13111.3134072447</v>
       </c>
       <c r="L6" t="n">
-        <v>-5000</v>
+        <v>-25129.52083279339</v>
       </c>
       <c r="M6" t="n">
-        <v>-245.3905487060547</v>
+        <v>0.06059407442808151</v>
       </c>
       <c r="N6" t="n">
-        <v>-244.078091506958</v>
+        <v>6.201607278782205</v>
       </c>
       <c r="O6" t="n">
+        <v>21</v>
+      </c>
+      <c r="P6" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>308.7509748</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1258.309154734619</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1212.756887117698</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.09135321113957628</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1302.402126194034</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1204.453236134671</v>
+      </c>
+      <c r="W6" t="n">
         <v>11</v>
       </c>
-      <c r="P6" t="n">
-        <v>209</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>276.8415416</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-500</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-500</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-500</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-500</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
       <c r="X6" t="n">
-        <v>-500</v>
+        <v>-1131.114301525041</v>
       </c>
       <c r="Y6" t="n">
-        <v>-500</v>
+        <v>-1253.427681164352</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>114.5046436055966</v>
       </c>
       <c r="AA6" t="n">
-        <v>-500</v>
+        <v>-1109.937787599805</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.699371195482236e-14</v>
+        <v>8.525799078304914</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.09135321113957628</v>
       </c>
       <c r="AF6" t="n">
-        <v>100</v>
+        <v>91.62936341716662</v>
       </c>
       <c r="AG6" t="n">
-        <v>-454.5454545454546</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>-1196.643849180638</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>11</v>
+      </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1187,12 +1193,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CartPole-v1</t>
+          <t>Pendulum-v1</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1200,98 +1206,94 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>run-20260729_170800-lrewprkz</t>
+          <t>run-20260729_143142-0xxw6y6p</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>500</v>
+        <v>-220.5741539286572</v>
       </c>
       <c r="F7" t="n">
-        <v>500</v>
+        <v>-197.8141914628206</v>
       </c>
       <c r="G7" t="n">
-        <v>9.538461538461538</v>
+        <v>-1162.450953943689</v>
       </c>
       <c r="H7" t="n">
-        <v>404.6985378258105</v>
+        <v>-359.1719996496569</v>
       </c>
       <c r="I7" t="n">
-        <v>500</v>
+        <v>-244.0348557501347</v>
       </c>
       <c r="J7" t="n">
-        <v>179.3174673016032</v>
+        <v>285.9389227629062</v>
       </c>
       <c r="K7" t="n">
-        <v>32154.75407946155</v>
+        <v>81761.06755081125</v>
       </c>
       <c r="L7" t="n">
-        <v>4196.914685314685</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.537583827972412</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.634163314868242</v>
-      </c>
+        <v>-3259.379442210054</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>3811</v>
+        <v>49901</v>
       </c>
       <c r="Q7" t="n">
-        <v>197.7475327</v>
+        <v>782.6554901</v>
       </c>
       <c r="R7" t="n">
-        <v>404.6985378258105</v>
+        <v>-359.1719996496569</v>
       </c>
       <c r="S7" t="n">
-        <v>297.4574424945094</v>
+        <v>-597.4437800681523</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4430889922779624</v>
+        <v>0.7961058296354292</v>
       </c>
       <c r="U7" t="n">
-        <v>298.7286865079349</v>
+        <v>-528.1511046256048</v>
       </c>
       <c r="V7" t="n">
-        <v>510.6683891436862</v>
+        <v>-190.1928946737091</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>475.4769230769231</v>
+        <v>-246.0460295868641</v>
       </c>
       <c r="Y7" t="n">
-        <v>404.6985378258105</v>
+        <v>-359.1719996496569</v>
       </c>
       <c r="Z7" t="n">
-        <v>179.3174673016032</v>
+        <v>285.9389227629062</v>
       </c>
       <c r="AA7" t="n">
-        <v>500</v>
+        <v>-197.8141914628206</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>41.06610298792118</v>
+        <v>49.90377853411189</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.4430889922779624</v>
+        <v>0.7961058296354292</v>
       </c>
       <c r="AF7" t="n">
-        <v>69.2957957098313</v>
+        <v>55.67600658603611</v>
       </c>
       <c r="AG7" t="n">
-        <v>381.5376986649713</v>
+        <v>-296.3072220190958</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -1307,7 +1309,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pendulum-v1</t>
+          <t>Acrobot-v1</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1315,77 +1317,77 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>run-20260729_142801-5u9s3kz8</t>
+          <t>run-20260729_154543-f2vuqnfe</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-1523.502741987067</v>
+        <v>-500</v>
       </c>
       <c r="F8" t="n">
-        <v>-1162.450953943689</v>
+        <v>-500</v>
       </c>
       <c r="G8" t="n">
-        <v>-1685.096704863287</v>
+        <v>-500</v>
       </c>
       <c r="H8" t="n">
-        <v>-1544.486089350468</v>
+        <v>-500</v>
       </c>
       <c r="I8" t="n">
-        <v>-1573.004482167475</v>
+        <v>-500</v>
       </c>
       <c r="J8" t="n">
-        <v>148.8201875346181</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>22147.44821783889</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-15646.37013488977</v>
+        <v>-5000</v>
       </c>
       <c r="M8" t="n">
-        <v>-92.08775329589844</v>
+        <v>-245.3905487060547</v>
       </c>
       <c r="N8" t="n">
-        <v>-94.59922480460925</v>
+        <v>-244.078091506958</v>
       </c>
       <c r="O8" t="n">
         <v>11</v>
       </c>
       <c r="P8" t="n">
-        <v>636</v>
+        <v>209</v>
       </c>
       <c r="Q8" t="n">
-        <v>147.9159561</v>
+        <v>276.8415416</v>
       </c>
       <c r="R8" t="n">
-        <v>-1544.486089350468</v>
+        <v>-500</v>
       </c>
       <c r="S8" t="n">
-        <v>-1429.320279131966</v>
+        <v>-500</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0963557966373166</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-1632.433200044468</v>
+        <v>-500</v>
       </c>
       <c r="V8" t="n">
-        <v>-1456.538978656468</v>
+        <v>-500</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1188.583241489669</v>
+        <v>-500</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1544.486089350468</v>
+        <v>-500</v>
       </c>
       <c r="Z8" t="n">
-        <v>148.8201875346181</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1162.450953943689</v>
+        <v>-500</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1394,20 +1396,20 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-22.58673080022005</v>
+        <v>-1.699371195482236e-14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0963557966373166</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>91.21126581964963</v>
+        <v>100</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1422.397284989979</v>
+        <v>-454.5454545454546</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -1415,7 +1417,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1428,7 +1430,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>run-20260729_153812-yzqbwz7d</t>
+          <t>run-20260806_105946-8yc9946w</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1453,22 +1455,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-5000</v>
+        <v>-10000</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1040128394961357</v>
+        <v>-73.86511993408203</v>
       </c>
       <c r="N9" t="n">
-        <v>881.3955829687608</v>
+        <v>-75.61802195072174</v>
       </c>
       <c r="O9" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P9" t="n">
-        <v>305</v>
+        <v>1017</v>
       </c>
       <c r="Q9" t="n">
-        <v>403.9623498</v>
+        <v>518.7850526</v>
       </c>
       <c r="R9" t="n">
         <v>-500</v>
@@ -1507,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.699371195482236e-14</v>
+        <v>-1.56864366397552e-15</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1516,7 +1518,7 @@
         <v>100</v>
       </c>
       <c r="AG9" t="n">
-        <v>-454.5454545454546</v>
+        <v>-476.1904761904762</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
@@ -1528,111 +1530,111 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CartPole-v1</t>
+          <t>Acrobot-v1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>run-20260729_171736-num3dzd1</t>
+          <t>run-20260806_233023-z82ovimx</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="F10" t="n">
-        <v>500</v>
+        <v>-218.2</v>
       </c>
       <c r="G10" t="n">
-        <v>9.538461538461538</v>
+        <v>-500</v>
       </c>
       <c r="H10" t="n">
-        <v>455.4125874125874</v>
+        <v>-436.015524093393</v>
       </c>
       <c r="I10" t="n">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="J10" t="n">
-        <v>147.879717925217</v>
+        <v>89.97879375570243</v>
       </c>
       <c r="K10" t="n">
-        <v>21868.41097364174</v>
+        <v>8096.183325731233</v>
       </c>
       <c r="L10" t="n">
-        <v>4754.76923076923</v>
+        <v>-26096.94696969697</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002900979307014495</v>
+        <v>-17.18779182434082</v>
       </c>
       <c r="N10" t="n">
-        <v>0.318675875103919</v>
+        <v>-17.54825510443213</v>
       </c>
       <c r="O10" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="P10" t="n">
-        <v>1635</v>
+        <v>3092</v>
       </c>
       <c r="Q10" t="n">
-        <v>353.1709708</v>
+        <v>1458.9859438</v>
       </c>
       <c r="R10" t="n">
-        <v>455.4125874125875</v>
+        <v>-359.1341666666667</v>
       </c>
       <c r="S10" t="n">
-        <v>319.7198053666789</v>
+        <v>-392.8985450929621</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3247159213700944</v>
+        <v>0.2063660323627131</v>
       </c>
       <c r="U10" t="n">
-        <v>368.0212587412587</v>
+        <v>-458.5959079581001</v>
       </c>
       <c r="V10" t="n">
-        <v>542.803916083916</v>
+        <v>-413.4351402286858</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="X10" t="n">
-        <v>475.4769230769231</v>
+        <v>-232.29</v>
       </c>
       <c r="Y10" t="n">
-        <v>455.4125874125874</v>
+        <v>-436.015524093393</v>
       </c>
       <c r="Z10" t="n">
-        <v>147.879717925217</v>
+        <v>89.97879375570243</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>-218.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="AD10" t="n">
-        <v>22.29370629370632</v>
+        <v>3.157559973078218</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.3247159213700944</v>
+        <v>0.2063660323627131</v>
       </c>
       <c r="AF10" t="n">
-        <v>75.48788263718797</v>
+        <v>82.89358065242128</v>
       </c>
       <c r="AG10" t="n">
-        <v>432.2517482517482</v>
+        <v>-427.8188027819175</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
@@ -1643,12 +1645,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MountainCar-v0</t>
+          <t>CartPole-v1</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1656,99 +1658,101 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>run-20260729_205322-kh3jwupp</t>
+          <t>run-20260729_170800-lrewprkz</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-200</v>
+        <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>-200</v>
+        <v>500</v>
       </c>
       <c r="G11" t="n">
-        <v>-200</v>
+        <v>9.538461538461538</v>
       </c>
       <c r="H11" t="n">
-        <v>-200</v>
+        <v>404.6985378258105</v>
       </c>
       <c r="I11" t="n">
-        <v>-200</v>
+        <v>500</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>179.3174673016032</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>32154.75407946155</v>
       </c>
       <c r="L11" t="n">
-        <v>-2000</v>
+        <v>4196.914685314685</v>
       </c>
       <c r="M11" t="n">
-        <v>2.021902084350586</v>
+        <v>1.537583827972412</v>
       </c>
       <c r="N11" t="n">
-        <v>895.325745533999</v>
+        <v>1.634163314868242</v>
       </c>
       <c r="O11" t="n">
         <v>11</v>
       </c>
       <c r="P11" t="n">
-        <v>449</v>
+        <v>3811</v>
       </c>
       <c r="Q11" t="n">
-        <v>264.3949611</v>
+        <v>197.7475327</v>
       </c>
       <c r="R11" t="n">
-        <v>-200</v>
+        <v>404.6985378258105</v>
       </c>
       <c r="S11" t="n">
-        <v>-200</v>
+        <v>297.4574424945094</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.4430889922779624</v>
       </c>
       <c r="U11" t="n">
-        <v>-200</v>
+        <v>298.7286865079349</v>
       </c>
       <c r="V11" t="n">
-        <v>-200</v>
+        <v>510.6683891436862</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
-        <v>-200</v>
+        <v>475.4769230769231</v>
       </c>
       <c r="Y11" t="n">
-        <v>-200</v>
+        <v>404.6985378258105</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>179.3174673016032</v>
       </c>
       <c r="AA11" t="n">
-        <v>-200</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.840691781539163e-16</v>
+        <v>41.06610298792118</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.4430889922779624</v>
       </c>
       <c r="AF11" t="n">
-        <v>100</v>
+        <v>69.2957957098313</v>
       </c>
       <c r="AG11" t="n">
-        <v>-181.8181818181818</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
+        <v>381.5376986649713</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3</v>
+      </c>
       <c r="AI11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
@@ -1756,7 +1760,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,99 +1773,97 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>run-20260729_142110-n1ypytca</t>
+          <t>run-20260729_142801-5u9s3kz8</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-318.0833972681257</v>
+        <v>-1523.502741987067</v>
       </c>
       <c r="F12" t="n">
-        <v>-287.7574936641852</v>
+        <v>-1162.450953943689</v>
       </c>
       <c r="G12" t="n">
-        <v>-1276.729204780413</v>
+        <v>-1685.096704863287</v>
       </c>
       <c r="H12" t="n">
-        <v>-821.2745780068734</v>
+        <v>-1544.486089350468</v>
       </c>
       <c r="I12" t="n">
-        <v>-921.8135992908541</v>
+        <v>-1573.004482167475</v>
       </c>
       <c r="J12" t="n">
-        <v>397.0416940626303</v>
+        <v>148.8201875346181</v>
       </c>
       <c r="K12" t="n">
-        <v>157642.1068241233</v>
+        <v>22147.44821783889</v>
       </c>
       <c r="L12" t="n">
-        <v>-8293.753182469702</v>
+        <v>-15646.37013488977</v>
       </c>
       <c r="M12" t="n">
-        <v>248.6179962158203</v>
+        <v>-92.08775329589844</v>
       </c>
       <c r="N12" t="n">
-        <v>1602.171272316957</v>
+        <v>-94.59922480460925</v>
       </c>
       <c r="O12" t="n">
         <v>11</v>
       </c>
       <c r="P12" t="n">
-        <v>449</v>
+        <v>636</v>
       </c>
       <c r="Q12" t="n">
-        <v>258.8843575</v>
+        <v>147.9159561</v>
       </c>
       <c r="R12" t="n">
-        <v>-821.2745780068734</v>
+        <v>-1544.486089350468</v>
       </c>
       <c r="S12" t="n">
-        <v>-861.3116178935904</v>
+        <v>-1429.320279131966</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4834457375098579</v>
+        <v>0.0963557966373166</v>
       </c>
       <c r="U12" t="n">
-        <v>-1055.911225066176</v>
+        <v>-1632.433200044468</v>
       </c>
       <c r="V12" t="n">
-        <v>-586.6379309475702</v>
+        <v>-1456.538978656468</v>
       </c>
       <c r="W12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-337.2060792199966</v>
+        <v>-1188.583241489669</v>
       </c>
       <c r="Y12" t="n">
-        <v>-821.2745780068734</v>
+        <v>-1544.486089350468</v>
       </c>
       <c r="Z12" t="n">
-        <v>397.0416940626303</v>
+        <v>148.8201875346181</v>
       </c>
       <c r="AA12" t="n">
-        <v>-287.7574936641852</v>
+        <v>-1162.450953943689</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>110.7684425076133</v>
+        <v>-22.58673080022005</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.4834457375098579</v>
+        <v>0.0963557966373166</v>
       </c>
       <c r="AF12" t="n">
-        <v>67.41062208845065</v>
+        <v>91.21126581964963</v>
       </c>
       <c r="AG12" t="n">
-        <v>-753.9775620427001</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>8</v>
-      </c>
+        <v>-1422.397284989979</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="b">
         <v>0</v>
       </c>
@@ -1871,12 +1873,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Acrobot-v1</t>
+          <t>Pendulum-v1</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1884,99 +1886,101 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>run-20260729_171141-3a01qt6l</t>
+          <t>run-20260806_144308-s7lcd065</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-500</v>
+        <v>-1262.748620411576</v>
       </c>
       <c r="F13" t="n">
-        <v>-500</v>
+        <v>-1115.163023310199</v>
       </c>
       <c r="G13" t="n">
-        <v>-500</v>
+        <v>-1436.160718018588</v>
       </c>
       <c r="H13" t="n">
-        <v>-500</v>
+        <v>-1226.620301670616</v>
       </c>
       <c r="I13" t="n">
-        <v>-500</v>
+        <v>-1212.438703117738</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>86.0813352213962</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>7409.996273498386</v>
       </c>
       <c r="L13" t="n">
-        <v>-5000</v>
+        <v>-24549.75291999763</v>
       </c>
       <c r="M13" t="n">
-        <v>0.008979347534477711</v>
+        <v>-0.5185821652412415</v>
       </c>
       <c r="N13" t="n">
-        <v>48.52327909202625</v>
+        <v>-0.5158981253703435</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
-        <v>305</v>
+        <v>896</v>
       </c>
       <c r="Q13" t="n">
-        <v>330.2886978</v>
+        <v>287.6810983</v>
       </c>
       <c r="R13" t="n">
-        <v>-500</v>
+        <v>-1230.161406266195</v>
       </c>
       <c r="S13" t="n">
-        <v>-500</v>
+        <v>-1211.647339713165</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.07017765408264996</v>
       </c>
       <c r="U13" t="n">
-        <v>-500</v>
+        <v>-1263.437896897608</v>
       </c>
       <c r="V13" t="n">
-        <v>-500</v>
+        <v>-1189.802706443623</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X13" t="n">
-        <v>-500</v>
+        <v>-1131.212908045619</v>
       </c>
       <c r="Y13" t="n">
-        <v>-500</v>
+        <v>-1226.620301670616</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>86.0813352213962</v>
       </c>
       <c r="AA13" t="n">
-        <v>-500</v>
+        <v>-1115.163023310199</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>-1.699371195482236e-14</v>
+        <v>1.409481204806761</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>0.07017765408264996</v>
       </c>
       <c r="AF13" t="n">
-        <v>100</v>
+        <v>93.44242950551926</v>
       </c>
       <c r="AG13" t="n">
-        <v>-454.5454545454546</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
+        <v>-1169.035853333221</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8</v>
+      </c>
       <c r="AI13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
@@ -1984,12 +1988,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MountainCar-v0</t>
+          <t>Pendulum-v1</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1997,99 +2001,101 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>run-20260729_204909-pgay1oio</t>
+          <t>run-20260806_151421-jwubf4go</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-200</v>
+        <v>-1262.748620411576</v>
       </c>
       <c r="F14" t="n">
-        <v>-200</v>
+        <v>-1115.163023310199</v>
       </c>
       <c r="G14" t="n">
-        <v>-200</v>
+        <v>-1436.160718018588</v>
       </c>
       <c r="H14" t="n">
-        <v>-200</v>
+        <v>-1226.620301670616</v>
       </c>
       <c r="I14" t="n">
-        <v>-200</v>
+        <v>-1212.438703117738</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>86.0813352213962</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>7409.996273498386</v>
       </c>
       <c r="L14" t="n">
-        <v>-2000</v>
+        <v>-24549.75291999763</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006548303179442883</v>
+        <v>-0.5185821652412415</v>
       </c>
       <c r="N14" t="n">
-        <v>71.73304060848238</v>
+        <v>-0.5158981253703435</v>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>449</v>
+        <v>896</v>
       </c>
       <c r="Q14" t="n">
-        <v>182.1001624</v>
+        <v>287.7698346</v>
       </c>
       <c r="R14" t="n">
-        <v>-200</v>
+        <v>-1230.161406266195</v>
       </c>
       <c r="S14" t="n">
-        <v>-200</v>
+        <v>-1211.647339713165</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.07017765408264996</v>
       </c>
       <c r="U14" t="n">
-        <v>-200</v>
+        <v>-1263.437896897608</v>
       </c>
       <c r="V14" t="n">
-        <v>-200</v>
+        <v>-1189.802706443623</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X14" t="n">
-        <v>-200</v>
+        <v>-1131.212908045619</v>
       </c>
       <c r="Y14" t="n">
-        <v>-200</v>
+        <v>-1226.620301670616</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>86.0813352213962</v>
       </c>
       <c r="AA14" t="n">
-        <v>-200</v>
+        <v>-1115.163023310199</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>-1.840691781539163e-16</v>
+        <v>1.409481204806761</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.07017765408264996</v>
       </c>
       <c r="AF14" t="n">
-        <v>100</v>
+        <v>93.44242950551926</v>
       </c>
       <c r="AG14" t="n">
-        <v>-181.8181818181818</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
+        <v>-1169.035853333221</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>8</v>
+      </c>
       <c r="AI14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
@@ -2097,12 +2103,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pendulum-v1</t>
+          <t>Acrobot-v1</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2110,101 +2116,99 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>run-20260729_141719-t7p5us0r</t>
+          <t>run-20260729_153812-yzqbwz7d</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-245.9180673140198</v>
+        <v>-500</v>
       </c>
       <c r="F15" t="n">
-        <v>-219.4573177568721</v>
+        <v>-500</v>
       </c>
       <c r="G15" t="n">
-        <v>-1162.450953943689</v>
+        <v>-500</v>
       </c>
       <c r="H15" t="n">
-        <v>-539.6959803689576</v>
+        <v>-500</v>
       </c>
       <c r="I15" t="n">
-        <v>-402.8396155024116</v>
+        <v>-500</v>
       </c>
       <c r="J15" t="n">
-        <v>351.3321372812916</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>123434.2706866403</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-5232.471273429679</v>
+        <v>-5000</v>
       </c>
       <c r="M15" t="n">
-        <v>74.09199523925781</v>
+        <v>0.1040128394961357</v>
       </c>
       <c r="N15" t="n">
-        <v>192.5587954423366</v>
+        <v>881.3955829687608</v>
       </c>
       <c r="O15" t="n">
         <v>11</v>
       </c>
       <c r="P15" t="n">
-        <v>449</v>
+        <v>305</v>
       </c>
       <c r="Q15" t="n">
-        <v>199.1797317</v>
+        <v>403.9623498</v>
       </c>
       <c r="R15" t="n">
-        <v>-539.6959803689576</v>
+        <v>-500</v>
       </c>
       <c r="S15" t="n">
-        <v>-697.6821874504836</v>
+        <v>-500</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6509815712192389</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-747.3200055748785</v>
+        <v>-500</v>
       </c>
       <c r="V15" t="n">
-        <v>-332.0719551630368</v>
+        <v>-500</v>
       </c>
       <c r="W15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-266.6069995662129</v>
+        <v>-500</v>
       </c>
       <c r="Y15" t="n">
-        <v>-539.6959803689576</v>
+        <v>-500</v>
       </c>
       <c r="Z15" t="n">
-        <v>351.3321372812916</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-219.4573177568721</v>
+        <v>-500</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>80.7308572839803</v>
+        <v>-1.699371195482236e-14</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.6509815712192389</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>60.5700280022815</v>
+        <v>100</v>
       </c>
       <c r="AG15" t="n">
-        <v>-475.6792066754253</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>5</v>
-      </c>
+        <v>-454.5454545454546</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
@@ -2212,12 +2216,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CartPole-v1</t>
+          <t>Acrobot-v1</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2225,94 +2229,98 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>run-20260729_163947-92lhukow</t>
+          <t>run-20260806_113207-u7kjh4ge</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="F16" t="n">
-        <v>500</v>
+        <v>-172.4</v>
       </c>
       <c r="G16" t="n">
-        <v>22.4</v>
+        <v>-500</v>
       </c>
       <c r="H16" t="n">
-        <v>443.109090909091</v>
+        <v>-481.1619047619047</v>
       </c>
       <c r="I16" t="n">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="J16" t="n">
-        <v>141.5030208479342</v>
+        <v>72.28188207421327</v>
       </c>
       <c r="K16" t="n">
-        <v>20023.10490909091</v>
+        <v>5224.670476190475</v>
       </c>
       <c r="L16" t="n">
-        <v>4613</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+        <v>-9604.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.142839789390564</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1920.488378657699</v>
+      </c>
       <c r="O16" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P16" t="n">
-        <v>49868</v>
+        <v>2041</v>
       </c>
       <c r="Q16" t="n">
-        <v>834.144583</v>
+        <v>711.0200708</v>
       </c>
       <c r="R16" t="n">
-        <v>443.1090909090909</v>
+        <v>-480.22</v>
       </c>
       <c r="S16" t="n">
-        <v>316.6004160543844</v>
+        <v>-493.577799089754</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3193412722759174</v>
+        <v>0.1502236177861604</v>
       </c>
       <c r="U16" t="n">
-        <v>359.4861493968461</v>
+        <v>-512.0773763866071</v>
       </c>
       <c r="V16" t="n">
-        <v>526.7320324213359</v>
+        <v>-450.2464331372024</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>476.12</v>
+        <v>-188.78</v>
       </c>
       <c r="Y16" t="n">
-        <v>443.109090909091</v>
+        <v>-481.1619047619047</v>
       </c>
       <c r="Z16" t="n">
-        <v>141.5030208479342</v>
+        <v>72.28188207421327</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>-172.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>23.35545454545455</v>
+        <v>-4.094025974025976</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.3193412722759174</v>
+        <v>0.1502236177861604</v>
       </c>
       <c r="AF16" t="n">
-        <v>75.79540040272971</v>
+        <v>86.93961630910549</v>
       </c>
       <c r="AG16" t="n">
-        <v>419.3636363636364</v>
+        <v>-457.3523809523809</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
@@ -2323,12 +2331,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pendulum-v1</t>
+          <t>CartPole-v1</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2336,94 +2344,98 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>run-20260729_113328-cyshpsut</t>
+          <t>run-20260729_171736-num3dzd1</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-218.3302575957343</v>
+        <v>500</v>
       </c>
       <c r="F17" t="n">
-        <v>-195.508550465746</v>
+        <v>500</v>
       </c>
       <c r="G17" t="n">
-        <v>-1155.753749675708</v>
+        <v>9.538461538461538</v>
       </c>
       <c r="H17" t="n">
-        <v>-341.7296554947541</v>
+        <v>455.4125874125874</v>
       </c>
       <c r="I17" t="n">
-        <v>-267.158253364485</v>
+        <v>500</v>
       </c>
       <c r="J17" t="n">
-        <v>274.3809319585858</v>
+        <v>147.879717925217</v>
       </c>
       <c r="K17" t="n">
-        <v>75284.8958224621</v>
+        <v>21868.41097364174</v>
       </c>
       <c r="L17" t="n">
-        <v>-3071.984206806574</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>4754.76923076923</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0002900979307014495</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.318675875103919</v>
+      </c>
       <c r="O17" t="n">
         <v>11</v>
       </c>
       <c r="P17" t="n">
-        <v>49901</v>
+        <v>1635</v>
       </c>
       <c r="Q17" t="n">
-        <v>1098.9359443</v>
+        <v>353.1709708</v>
       </c>
       <c r="R17" t="n">
-        <v>-341.7296554947541</v>
+        <v>455.4125874125875</v>
       </c>
       <c r="S17" t="n">
-        <v>-586.9318502204624</v>
+        <v>319.7198053666789</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8029181183041865</v>
+        <v>0.3247159213700944</v>
       </c>
       <c r="U17" t="n">
-        <v>-503.8784243885669</v>
+        <v>368.0212587412587</v>
       </c>
       <c r="V17" t="n">
-        <v>-179.5808866009412</v>
+        <v>542.803916083916</v>
       </c>
       <c r="W17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>-243.5208104262441</v>
+        <v>475.4769230769231</v>
       </c>
       <c r="Y17" t="n">
-        <v>-341.7296554947541</v>
+        <v>455.4125874125874</v>
       </c>
       <c r="Z17" t="n">
-        <v>274.3809319585858</v>
+        <v>147.879717925217</v>
       </c>
       <c r="AA17" t="n">
-        <v>-195.508550465746</v>
+        <v>500</v>
       </c>
       <c r="AB17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>44.99462884190318</v>
+        <v>22.29370629370632</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.8029181183041865</v>
+        <v>0.3247159213700944</v>
       </c>
       <c r="AF17" t="n">
-        <v>55.46563595137608</v>
+        <v>75.48788263718797</v>
       </c>
       <c r="AG17" t="n">
-        <v>-279.2712915278703</v>
+        <v>432.2517482517482</v>
       </c>
       <c r="AH17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="b">
         <v>0</v>
@@ -2434,12 +2446,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TD3</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pendulum-v1</t>
+          <t>MountainCar-v0</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2447,100 +2459,1460 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>run-20260729_111932-9hz3to4q</t>
+          <t>run-20260729_205322-kh3jwupp</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-207.5724532386165</v>
+        <v>-200</v>
       </c>
       <c r="F18" t="n">
-        <v>-197.949015942858</v>
+        <v>-200</v>
       </c>
       <c r="G18" t="n">
-        <v>-1162.450953943689</v>
+        <v>-200</v>
       </c>
       <c r="H18" t="n">
-        <v>-413.0663914181831</v>
+        <v>-200</v>
       </c>
       <c r="I18" t="n">
-        <v>-263.0956040927571</v>
+        <v>-200</v>
       </c>
       <c r="J18" t="n">
-        <v>350.17242888629</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>122620.7299521239</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-3858.718602008862</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>-2000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.021902084350586</v>
+      </c>
+      <c r="N18" t="n">
+        <v>895.325745533999</v>
+      </c>
       <c r="O18" t="n">
         <v>11</v>
       </c>
       <c r="P18" t="n">
-        <v>49802</v>
+        <v>449</v>
       </c>
       <c r="Q18" t="n">
-        <v>811.8702804</v>
+        <v>264.3949611</v>
       </c>
       <c r="R18" t="n">
-        <v>-413.0663914181831</v>
+        <v>-200</v>
       </c>
       <c r="S18" t="n">
-        <v>-618.8104705500274</v>
+        <v>-200</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8477388530304806</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-620.0050727586137</v>
+        <v>-200</v>
       </c>
       <c r="V18" t="n">
-        <v>-206.1277100777525</v>
+        <v>-200</v>
       </c>
       <c r="W18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-246.1741128428996</v>
+        <v>-200</v>
       </c>
       <c r="Y18" t="n">
-        <v>-413.0663914181831</v>
+        <v>-200</v>
       </c>
       <c r="Z18" t="n">
-        <v>350.17242888629</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>-197.949015942858</v>
+        <v>-200</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>74.44280014425429</v>
+        <v>-1.840691781539163e-16</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.8477388530304806</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>54.12020201663768</v>
+        <v>100</v>
       </c>
       <c r="AG18" t="n">
-        <v>-350.7926001826238</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>5</v>
-      </c>
+        <v>-181.8181818181818</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MountainCar-v0</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>run-20260806_160343-r2g5psh1</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.150246262550354</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1606.367472619675</v>
+      </c>
+      <c r="O19" t="n">
+        <v>41</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1241</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>880.1615329</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-200</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-3.555082100765894e-16</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-195.1219512195122</v>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>run-20260729_142110-n1ypytca</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>-318.0833972681257</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-287.7574936641852</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1276.729204780413</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-821.2745780068734</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-921.8135992908541</v>
+      </c>
+      <c r="J20" t="n">
+        <v>397.0416940626303</v>
+      </c>
+      <c r="K20" t="n">
+        <v>157642.1068241233</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-8293.753182469702</v>
+      </c>
+      <c r="M20" t="n">
+        <v>248.6179962158203</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1602.171272316957</v>
+      </c>
+      <c r="O20" t="n">
+        <v>11</v>
+      </c>
+      <c r="P20" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>258.8843575</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-821.2745780068734</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-861.3116178935904</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.4834457375098579</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-1055.911225066176</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-586.6379309475702</v>
+      </c>
+      <c r="W20" t="n">
+        <v>8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-337.2060792199966</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-821.2745780068734</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>397.0416940626303</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-287.7574936641852</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>110.7684425076133</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.4834457375098579</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>67.41062208845065</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-753.9775620427001</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>run-20260806_153621-k6y8llea</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>-326.4612258855022</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-205.9221520456136</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1155.798209759019</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-436.9015439899808</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-277.6784635508047</v>
+      </c>
+      <c r="J21" t="n">
+        <v>321.3715533320886</v>
+      </c>
+      <c r="K21" t="n">
+        <v>103279.6752910795</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-8433.802705967337</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.004880172200500965</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6.20248047688376</v>
+      </c>
+      <c r="O21" t="n">
+        <v>21</v>
+      </c>
+      <c r="P21" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>498.1407452</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-400.9567107015288</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-433.0586684148304</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.7355697359116188</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-574.3544277959653</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-299.4486601839963</v>
+      </c>
+      <c r="W21" t="n">
+        <v>6</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-253.415954931284</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-436.9015439899808</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>321.3715533320886</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-205.9221520456136</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>37.53842683855429</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.7355697359116188</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>57.61796713254762</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-401.6096526651113</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Acrobot-v1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>run-20260729_171141-3a01qt6l</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.008979347534477711</v>
+      </c>
+      <c r="N22" t="n">
+        <v>48.52327909202625</v>
+      </c>
+      <c r="O22" t="n">
+        <v>11</v>
+      </c>
+      <c r="P22" t="n">
+        <v>305</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>330.2886978</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-500</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-1.699371195482236e-14</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-454.5454545454546</v>
+      </c>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Acrobot-v1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>run-20260806_112218-zln9xopa</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.03051353991031647</v>
+      </c>
+      <c r="N23" t="n">
+        <v>693.2853104208596</v>
+      </c>
+      <c r="O23" t="n">
+        <v>21</v>
+      </c>
+      <c r="P23" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>557.7023058</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-1.56864366397552e-15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-476.1904761904762</v>
+      </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MountainCar-v0</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>run-20260729_204909-pgay1oio</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.006548303179442883</v>
+      </c>
+      <c r="N24" t="n">
+        <v>71.73304060848238</v>
+      </c>
+      <c r="O24" t="n">
+        <v>11</v>
+      </c>
+      <c r="P24" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>182.1001624</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-200</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-1.840691781539163e-16</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-181.8181818181818</v>
+      </c>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MountainCar-v0</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>run-20260806_155127-hzh7i4t3</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.002150806365534663</v>
+      </c>
+      <c r="N25" t="n">
+        <v>64.25386444770818</v>
+      </c>
+      <c r="O25" t="n">
+        <v>41</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1241</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>599.8824757</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-200</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-3.555082100765894e-16</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-195.1219512195122</v>
+      </c>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>run-20260729_141719-t7p5us0r</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-245.9180673140198</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-219.4573177568721</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1162.450953943689</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-539.6959803689576</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-402.8396155024116</v>
+      </c>
+      <c r="J26" t="n">
+        <v>351.3321372812916</v>
+      </c>
+      <c r="K26" t="n">
+        <v>123434.2706866403</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-5232.471273429679</v>
+      </c>
+      <c r="M26" t="n">
+        <v>74.09199523925781</v>
+      </c>
+      <c r="N26" t="n">
+        <v>192.5587954423366</v>
+      </c>
+      <c r="O26" t="n">
+        <v>11</v>
+      </c>
+      <c r="P26" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>199.1797317</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-539.6959803689576</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-697.6821874504836</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.6509815712192389</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-747.3200055748785</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-332.0719551630368</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-266.6069995662129</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-539.6959803689576</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>351.3321372812916</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-219.4573177568721</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>80.7308572839803</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.6509815712192389</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>60.5700280022815</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>-475.6792066754253</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>run-20260806_152834-xy4luccb</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-311.4664162905647</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-197.9138957092919</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1155.798209759019</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-347.0494662007257</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-276.0082766384609</v>
+      </c>
+      <c r="J27" t="n">
+        <v>240.2571253039864</v>
+      </c>
+      <c r="K27" t="n">
+        <v>57723.48625933543</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-6554.406477190447</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.01735409535467625</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.645528168181698</v>
+      </c>
+      <c r="O27" t="n">
+        <v>21</v>
+      </c>
+      <c r="P27" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>427.8886858</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-306.6120290228109</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-397.9564814102443</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.692284958493574</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-449.8091360768065</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-244.289796324645</v>
+      </c>
+      <c r="W27" t="n">
+        <v>5</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-245.8081114117782</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-347.0494662007257</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>240.2571253039864</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-197.9138957092919</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>21.07368615209907</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.692284958493574</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>59.09170290623943</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-312.114594151926</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CartPole-v1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>run-20260729_163947-92lhukow</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>500</v>
+      </c>
+      <c r="F28" t="n">
+        <v>500</v>
+      </c>
+      <c r="G28" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>443.109090909091</v>
+      </c>
+      <c r="I28" t="n">
+        <v>500</v>
+      </c>
+      <c r="J28" t="n">
+        <v>141.5030208479342</v>
+      </c>
+      <c r="K28" t="n">
+        <v>20023.10490909091</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4613</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>11</v>
+      </c>
+      <c r="P28" t="n">
+        <v>49868</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>834.144583</v>
+      </c>
+      <c r="R28" t="n">
+        <v>443.1090909090909</v>
+      </c>
+      <c r="S28" t="n">
+        <v>316.6004160543844</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.3193412722759174</v>
+      </c>
+      <c r="U28" t="n">
+        <v>359.4861493968461</v>
+      </c>
+      <c r="V28" t="n">
+        <v>526.7320324213359</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2</v>
+      </c>
+      <c r="X28" t="n">
+        <v>476.12</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>443.109090909091</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>141.5030208479342</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>23.35545454545455</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.3193412722759174</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>75.79540040272971</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>419.3636363636364</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>run-20260729_113328-cyshpsut</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-218.3302575957343</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-195.508550465746</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-1155.753749675708</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-341.7296554947541</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-267.158253364485</v>
+      </c>
+      <c r="J29" t="n">
+        <v>274.3809319585858</v>
+      </c>
+      <c r="K29" t="n">
+        <v>75284.8958224621</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-3071.984206806574</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>11</v>
+      </c>
+      <c r="P29" t="n">
+        <v>49901</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1098.9359443</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-341.7296554947541</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-586.9318502204624</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.8029181183041865</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-503.8784243885669</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-179.5808866009412</v>
+      </c>
+      <c r="W29" t="n">
+        <v>5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-243.5208104262441</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-341.7296554947541</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>274.3809319585858</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-195.508550465746</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>44.99462884190318</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.8029181183041865</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>55.46563595137608</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>-279.2712915278703</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>run-20260729_111932-9hz3to4q</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>-207.5724532386165</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-197.949015942858</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1162.450953943689</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-413.0663914181831</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-263.0956040927571</v>
+      </c>
+      <c r="J30" t="n">
+        <v>350.17242888629</v>
+      </c>
+      <c r="K30" t="n">
+        <v>122620.7299521239</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-3858.718602008862</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>11</v>
+      </c>
+      <c r="P30" t="n">
+        <v>49802</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>811.8702804</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-413.0663914181831</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-618.8104705500274</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.8477388530304806</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-620.0050727586137</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-206.1277100777525</v>
+      </c>
+      <c r="W30" t="n">
+        <v>5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-246.1741128428996</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-413.0663914181831</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>350.17242888629</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-197.949015942858</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>74.44280014425429</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.8477388530304806</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>54.12020201663768</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>-350.7926001826238</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2553,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2859,7 +4231,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2872,97 +4244,99 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>run-20260729_154543-f2vuqnfe</t>
+          <t>run-20260806_111231-qnts3ypd</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>-500</v>
       </c>
       <c r="F3" t="n">
-        <v>-500</v>
+        <v>-485.1</v>
       </c>
       <c r="G3" t="n">
         <v>-500</v>
       </c>
       <c r="H3" t="n">
-        <v>-500</v>
+        <v>-498.2142857142857</v>
       </c>
       <c r="I3" t="n">
         <v>-500</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3.842302137298117</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>14.76328571428568</v>
       </c>
       <c r="L3" t="n">
-        <v>-5000</v>
+        <v>-9962.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-245.3905487060547</v>
+        <v>4483.95068359375</v>
       </c>
       <c r="N3" t="n">
-        <v>-244.078091506958</v>
+        <v>4788.676675186157</v>
       </c>
       <c r="O3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1113</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>547.3053036</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-498.125</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-498.7420775286257</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.007712147659092994</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-499.8576654837446</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-496.5709059448268</v>
+      </c>
+      <c r="W3" t="n">
         <v>11</v>
       </c>
-      <c r="P3" t="n">
-        <v>209</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>276.8415416</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-500</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-500</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-500</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-500</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
       <c r="X3" t="n">
-        <v>-500</v>
+        <v>-485.845</v>
       </c>
       <c r="Y3" t="n">
-        <v>-500</v>
+        <v>-498.2142857142857</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.842302137298117</v>
       </c>
       <c r="AA3" t="n">
-        <v>-500</v>
+        <v>-485.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.699371195482236e-14</v>
+        <v>-0.02701298701299018</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.007712147659092994</v>
       </c>
       <c r="AF3" t="n">
-        <v>100</v>
+        <v>99.23468743757748</v>
       </c>
       <c r="AG3" t="n">
-        <v>-454.5454545454546</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>-474.4047619047619</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>11</v>
+      </c>
       <c r="AI3" t="b">
         <v>1</v>
       </c>
@@ -2972,7 +4346,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2985,7 +4359,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>run-20260729_153812-yzqbwz7d</t>
+          <t>run-20260729_154543-f2vuqnfe</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -3013,19 +4387,19 @@
         <v>-5000</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1040128394961357</v>
+        <v>-245.3905487060547</v>
       </c>
       <c r="N4" t="n">
-        <v>881.3955829687608</v>
+        <v>-244.078091506958</v>
       </c>
       <c r="O4" t="n">
         <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>305</v>
+        <v>209</v>
       </c>
       <c r="Q4" t="n">
-        <v>403.9623498</v>
+        <v>276.8415416</v>
       </c>
       <c r="R4" t="n">
         <v>-500</v>
@@ -3085,7 +4459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3098,7 +4472,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>run-20260729_171141-3a01qt6l</t>
+          <t>run-20260806_105946-8yc9946w</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -3123,22 +4497,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-5000</v>
+        <v>-10000</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008979347534477711</v>
+        <v>-73.86511993408203</v>
       </c>
       <c r="N5" t="n">
-        <v>48.52327909202625</v>
+        <v>-75.61802195072174</v>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
-        <v>305</v>
+        <v>1017</v>
       </c>
       <c r="Q5" t="n">
-        <v>330.2886978</v>
+        <v>518.7850526</v>
       </c>
       <c r="R5" t="n">
         <v>-500</v>
@@ -3177,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.699371195482236e-14</v>
+        <v>-1.56864366397552e-15</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -3186,7 +4560,7 @@
         <v>100</v>
       </c>
       <c r="AG5" t="n">
-        <v>-454.5454545454546</v>
+        <v>-476.1904761904762</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
@@ -3194,6 +4568,575 @@
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Acrobot-v1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>run-20260806_233023-z82ovimx</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-218.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-436.015524093393</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-500</v>
+      </c>
+      <c r="J6" t="n">
+        <v>89.97879375570243</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8096.183325731233</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-26096.94696969697</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-17.18779182434082</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-17.54825510443213</v>
+      </c>
+      <c r="O6" t="n">
+        <v>61</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3092</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1458.9859438</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-359.1341666666667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-392.8985450929621</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2063660323627131</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-458.5959079581001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-413.4351402286858</v>
+      </c>
+      <c r="W6" t="n">
+        <v>46</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-232.29</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-436.015524093393</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>89.97879375570243</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-218.2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.157559973078218</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2063660323627131</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>82.89358065242128</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-427.8188027819175</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Acrobot-v1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>run-20260729_153812-yzqbwz7d</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1040128394961357</v>
+      </c>
+      <c r="N7" t="n">
+        <v>881.3955829687608</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11</v>
+      </c>
+      <c r="P7" t="n">
+        <v>305</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>403.9623498</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-500</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1.699371195482236e-14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-454.5454545454546</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Acrobot-v1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>run-20260806_113207-u7kjh4ge</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-172.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-481.1619047619047</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-500</v>
+      </c>
+      <c r="J8" t="n">
+        <v>72.28188207421327</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5224.670476190475</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-9604.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.142839789390564</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1920.488378657699</v>
+      </c>
+      <c r="O8" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2041</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>711.0200708</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-480.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-493.577799089754</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1502236177861604</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-512.0773763866071</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-450.2464331372024</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-188.78</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-481.1619047619047</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>72.28188207421327</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-172.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-4.094025974025976</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1502236177861604</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>86.93961630910549</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-457.3523809523809</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Acrobot-v1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>run-20260729_171141-3a01qt6l</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.008979347534477711</v>
+      </c>
+      <c r="N9" t="n">
+        <v>48.52327909202625</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>305</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>330.2886978</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1.699371195482236e-14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-454.5454545454546</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Acrobot-v1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>run-20260806_112218-zln9xopa</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.03051353991031647</v>
+      </c>
+      <c r="N10" t="n">
+        <v>693.2853104208596</v>
+      </c>
+      <c r="O10" t="n">
+        <v>21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>557.7023058</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-500</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-1.56864366397552e-15</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-476.1904761904762</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3863,7 +5806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4169,7 +6112,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DDPG</t>
+          <t>A2C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4182,94 +6125,98 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>run-20260729_143142-0xxw6y6p</t>
+          <t>run-20260806_152025-lrqwmvdy</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-220.5741539286572</v>
+        <v>-1229.122733557015</v>
       </c>
       <c r="F3" t="n">
-        <v>-197.8141914628206</v>
+        <v>-1109.937787599805</v>
       </c>
       <c r="G3" t="n">
-        <v>-1162.450953943689</v>
+        <v>-1533.468066104518</v>
       </c>
       <c r="H3" t="n">
-        <v>-359.1719996496569</v>
+        <v>-1253.427681164352</v>
       </c>
       <c r="I3" t="n">
-        <v>-244.0348557501347</v>
+        <v>-1229.122733557015</v>
       </c>
       <c r="J3" t="n">
-        <v>285.9389227629062</v>
+        <v>114.5046436055966</v>
       </c>
       <c r="K3" t="n">
-        <v>81761.06755081125</v>
+        <v>13111.3134072447</v>
       </c>
       <c r="L3" t="n">
-        <v>-3259.379442210054</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>-25129.52083279339</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.06059407442808151</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.201607278782205</v>
+      </c>
       <c r="O3" t="n">
+        <v>21</v>
+      </c>
+      <c r="P3" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>308.7509748</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-1258.309154734619</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-1212.756887117698</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.09135321113957628</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-1302.402126194034</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-1204.453236134671</v>
+      </c>
+      <c r="W3" t="n">
         <v>11</v>
       </c>
-      <c r="P3" t="n">
-        <v>49901</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>782.6554901</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-359.1719996496569</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-597.4437800681523</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.7961058296354292</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-528.1511046256048</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-190.1928946737091</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
       <c r="X3" t="n">
-        <v>-246.0460295868641</v>
+        <v>-1131.114301525041</v>
       </c>
       <c r="Y3" t="n">
-        <v>-359.1719996496569</v>
+        <v>-1253.427681164352</v>
       </c>
       <c r="Z3" t="n">
-        <v>285.9389227629062</v>
+        <v>114.5046436055966</v>
       </c>
       <c r="AA3" t="n">
-        <v>-197.8141914628206</v>
+        <v>-1109.937787599805</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>49.90377853411189</v>
+        <v>8.525799078304914</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.7961058296354292</v>
+        <v>0.09135321113957628</v>
       </c>
       <c r="AF3" t="n">
-        <v>55.67600658603611</v>
+        <v>91.62936341716662</v>
       </c>
       <c r="AG3" t="n">
-        <v>-296.3072220190958</v>
+        <v>-1196.643849180638</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="b">
         <v>0</v>
@@ -4280,7 +6227,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>DDPG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4293,97 +6240,95 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>run-20260729_142801-5u9s3kz8</t>
+          <t>run-20260729_143142-0xxw6y6p</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-1523.502741987067</v>
+        <v>-220.5741539286572</v>
       </c>
       <c r="F4" t="n">
+        <v>-197.8141914628206</v>
+      </c>
+      <c r="G4" t="n">
         <v>-1162.450953943689</v>
       </c>
-      <c r="G4" t="n">
-        <v>-1685.096704863287</v>
-      </c>
       <c r="H4" t="n">
-        <v>-1544.486089350468</v>
+        <v>-359.1719996496569</v>
       </c>
       <c r="I4" t="n">
-        <v>-1573.004482167475</v>
+        <v>-244.0348557501347</v>
       </c>
       <c r="J4" t="n">
-        <v>148.8201875346181</v>
+        <v>285.9389227629062</v>
       </c>
       <c r="K4" t="n">
-        <v>22147.44821783889</v>
+        <v>81761.06755081125</v>
       </c>
       <c r="L4" t="n">
-        <v>-15646.37013488977</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-92.08775329589844</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-94.59922480460925</v>
-      </c>
+        <v>-3259.379442210054</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>636</v>
+        <v>49901</v>
       </c>
       <c r="Q4" t="n">
-        <v>147.9159561</v>
+        <v>782.6554901</v>
       </c>
       <c r="R4" t="n">
-        <v>-1544.486089350468</v>
+        <v>-359.1719996496569</v>
       </c>
       <c r="S4" t="n">
-        <v>-1429.320279131966</v>
+        <v>-597.4437800681523</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0963557966373166</v>
+        <v>0.7961058296354292</v>
       </c>
       <c r="U4" t="n">
-        <v>-1632.433200044468</v>
+        <v>-528.1511046256048</v>
       </c>
       <c r="V4" t="n">
-        <v>-1456.538978656468</v>
+        <v>-190.1928946737091</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-1188.583241489669</v>
+        <v>-246.0460295868641</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1544.486089350468</v>
+        <v>-359.1719996496569</v>
       </c>
       <c r="Z4" t="n">
-        <v>148.8201875346181</v>
+        <v>285.9389227629062</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1162.450953943689</v>
+        <v>-197.8141914628206</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>-22.58673080022005</v>
+        <v>49.90377853411189</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0963557966373166</v>
+        <v>0.7961058296354292</v>
       </c>
       <c r="AF4" t="n">
-        <v>91.21126581964963</v>
+        <v>55.67600658603611</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1422.397284989979</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>-296.3072220190958</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
       <c r="AI4" t="b">
         <v>0</v>
       </c>
@@ -4393,7 +6338,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4406,99 +6351,97 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>run-20260729_142110-n1ypytca</t>
+          <t>run-20260729_142801-5u9s3kz8</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-318.0833972681257</v>
+        <v>-1523.502741987067</v>
       </c>
       <c r="F5" t="n">
-        <v>-287.7574936641852</v>
+        <v>-1162.450953943689</v>
       </c>
       <c r="G5" t="n">
-        <v>-1276.729204780413</v>
+        <v>-1685.096704863287</v>
       </c>
       <c r="H5" t="n">
-        <v>-821.2745780068734</v>
+        <v>-1544.486089350468</v>
       </c>
       <c r="I5" t="n">
-        <v>-921.8135992908541</v>
+        <v>-1573.004482167475</v>
       </c>
       <c r="J5" t="n">
-        <v>397.0416940626303</v>
+        <v>148.8201875346181</v>
       </c>
       <c r="K5" t="n">
-        <v>157642.1068241233</v>
+        <v>22147.44821783889</v>
       </c>
       <c r="L5" t="n">
-        <v>-8293.753182469702</v>
+        <v>-15646.37013488977</v>
       </c>
       <c r="M5" t="n">
-        <v>248.6179962158203</v>
+        <v>-92.08775329589844</v>
       </c>
       <c r="N5" t="n">
-        <v>1602.171272316957</v>
+        <v>-94.59922480460925</v>
       </c>
       <c r="O5" t="n">
         <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>449</v>
+        <v>636</v>
       </c>
       <c r="Q5" t="n">
-        <v>258.8843575</v>
+        <v>147.9159561</v>
       </c>
       <c r="R5" t="n">
-        <v>-821.2745780068734</v>
+        <v>-1544.486089350468</v>
       </c>
       <c r="S5" t="n">
-        <v>-861.3116178935904</v>
+        <v>-1429.320279131966</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4834457375098579</v>
+        <v>0.0963557966373166</v>
       </c>
       <c r="U5" t="n">
-        <v>-1055.911225066176</v>
+        <v>-1632.433200044468</v>
       </c>
       <c r="V5" t="n">
-        <v>-586.6379309475702</v>
+        <v>-1456.538978656468</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-337.2060792199966</v>
+        <v>-1188.583241489669</v>
       </c>
       <c r="Y5" t="n">
-        <v>-821.2745780068734</v>
+        <v>-1544.486089350468</v>
       </c>
       <c r="Z5" t="n">
-        <v>397.0416940626303</v>
+        <v>148.8201875346181</v>
       </c>
       <c r="AA5" t="n">
-        <v>-287.7574936641852</v>
+        <v>-1162.450953943689</v>
       </c>
       <c r="AB5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>110.7684425076133</v>
+        <v>-22.58673080022005</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4834457375098579</v>
+        <v>0.0963557966373166</v>
       </c>
       <c r="AF5" t="n">
-        <v>67.41062208845065</v>
+        <v>91.21126581964963</v>
       </c>
       <c r="AG5" t="n">
-        <v>-753.9775620427001</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>8</v>
-      </c>
+        <v>-1422.397284989979</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
         <v>0</v>
       </c>
@@ -4508,7 +6451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4521,77 +6464,77 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>run-20260729_141719-t7p5us0r</t>
+          <t>run-20260806_144308-s7lcd065</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>-245.9180673140198</v>
+        <v>-1262.748620411576</v>
       </c>
       <c r="F6" t="n">
-        <v>-219.4573177568721</v>
+        <v>-1115.163023310199</v>
       </c>
       <c r="G6" t="n">
-        <v>-1162.450953943689</v>
+        <v>-1436.160718018588</v>
       </c>
       <c r="H6" t="n">
-        <v>-539.6959803689576</v>
+        <v>-1226.620301670616</v>
       </c>
       <c r="I6" t="n">
-        <v>-402.8396155024116</v>
+        <v>-1212.438703117738</v>
       </c>
       <c r="J6" t="n">
-        <v>351.3321372812916</v>
+        <v>86.0813352213962</v>
       </c>
       <c r="K6" t="n">
-        <v>123434.2706866403</v>
+        <v>7409.996273498386</v>
       </c>
       <c r="L6" t="n">
-        <v>-5232.471273429679</v>
+        <v>-24549.75291999763</v>
       </c>
       <c r="M6" t="n">
-        <v>74.09199523925781</v>
+        <v>-0.5185821652412415</v>
       </c>
       <c r="N6" t="n">
-        <v>192.5587954423366</v>
+        <v>-0.5158981253703435</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P6" t="n">
-        <v>449</v>
+        <v>896</v>
       </c>
       <c r="Q6" t="n">
-        <v>199.1797317</v>
+        <v>287.6810983</v>
       </c>
       <c r="R6" t="n">
-        <v>-539.6959803689576</v>
+        <v>-1230.161406266195</v>
       </c>
       <c r="S6" t="n">
-        <v>-697.6821874504836</v>
+        <v>-1211.647339713165</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6509815712192389</v>
+        <v>0.07017765408264996</v>
       </c>
       <c r="U6" t="n">
-        <v>-747.3200055748785</v>
+        <v>-1263.437896897608</v>
       </c>
       <c r="V6" t="n">
-        <v>-332.0719551630368</v>
+        <v>-1189.802706443623</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>-266.6069995662129</v>
+        <v>-1131.212908045619</v>
       </c>
       <c r="Y6" t="n">
-        <v>-539.6959803689576</v>
+        <v>-1226.620301670616</v>
       </c>
       <c r="Z6" t="n">
-        <v>351.3321372812916</v>
+        <v>86.0813352213962</v>
       </c>
       <c r="AA6" t="n">
-        <v>-219.4573177568721</v>
+        <v>-1115.163023310199</v>
       </c>
       <c r="AB6" t="n">
         <v>8</v>
@@ -4600,19 +6543,19 @@
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>80.7308572839803</v>
+        <v>1.409481204806761</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6509815712192389</v>
+        <v>0.07017765408264996</v>
       </c>
       <c r="AF6" t="n">
-        <v>60.5700280022815</v>
+        <v>93.44242950551926</v>
       </c>
       <c r="AG6" t="n">
-        <v>-475.6792066754253</v>
+        <v>-1169.035853333221</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -4623,7 +6566,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4636,73 +6579,77 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>run-20260729_113328-cyshpsut</t>
+          <t>run-20260806_151421-jwubf4go</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>-218.3302575957343</v>
+        <v>-1262.748620411576</v>
       </c>
       <c r="F7" t="n">
-        <v>-195.508550465746</v>
+        <v>-1115.163023310199</v>
       </c>
       <c r="G7" t="n">
-        <v>-1155.753749675708</v>
+        <v>-1436.160718018588</v>
       </c>
       <c r="H7" t="n">
-        <v>-341.7296554947541</v>
+        <v>-1226.620301670616</v>
       </c>
       <c r="I7" t="n">
-        <v>-267.158253364485</v>
+        <v>-1212.438703117738</v>
       </c>
       <c r="J7" t="n">
-        <v>274.3809319585858</v>
+        <v>86.0813352213962</v>
       </c>
       <c r="K7" t="n">
-        <v>75284.8958224621</v>
+        <v>7409.996273498386</v>
       </c>
       <c r="L7" t="n">
-        <v>-3071.984206806574</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>-24549.75291999763</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.5185821652412415</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.5158981253703435</v>
+      </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>49901</v>
+        <v>896</v>
       </c>
       <c r="Q7" t="n">
-        <v>1098.9359443</v>
+        <v>287.7698346</v>
       </c>
       <c r="R7" t="n">
-        <v>-341.7296554947541</v>
+        <v>-1230.161406266195</v>
       </c>
       <c r="S7" t="n">
-        <v>-586.9318502204624</v>
+        <v>-1211.647339713165</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8029181183041865</v>
+        <v>0.07017765408264996</v>
       </c>
       <c r="U7" t="n">
-        <v>-503.8784243885669</v>
+        <v>-1263.437896897608</v>
       </c>
       <c r="V7" t="n">
-        <v>-179.5808866009412</v>
+        <v>-1189.802706443623</v>
       </c>
       <c r="W7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
-        <v>-243.5208104262441</v>
+        <v>-1131.212908045619</v>
       </c>
       <c r="Y7" t="n">
-        <v>-341.7296554947541</v>
+        <v>-1226.620301670616</v>
       </c>
       <c r="Z7" t="n">
-        <v>274.3809319585858</v>
+        <v>86.0813352213962</v>
       </c>
       <c r="AA7" t="n">
-        <v>-195.508550465746</v>
+        <v>-1115.163023310199</v>
       </c>
       <c r="AB7" t="n">
         <v>8</v>
@@ -4711,19 +6658,19 @@
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>44.99462884190318</v>
+        <v>1.409481204806761</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.8029181183041865</v>
+        <v>0.07017765408264996</v>
       </c>
       <c r="AF7" t="n">
-        <v>55.46563595137608</v>
+        <v>93.44242950551926</v>
       </c>
       <c r="AG7" t="n">
-        <v>-279.2712915278703</v>
+        <v>-1169.035853333221</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4734,7 +6681,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TD3</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4747,73 +6694,77 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>run-20260729_111932-9hz3to4q</t>
+          <t>run-20260729_142110-n1ypytca</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-207.5724532386165</v>
+        <v>-318.0833972681257</v>
       </c>
       <c r="F8" t="n">
-        <v>-197.949015942858</v>
+        <v>-287.7574936641852</v>
       </c>
       <c r="G8" t="n">
-        <v>-1162.450953943689</v>
+        <v>-1276.729204780413</v>
       </c>
       <c r="H8" t="n">
-        <v>-413.0663914181831</v>
+        <v>-821.2745780068734</v>
       </c>
       <c r="I8" t="n">
-        <v>-263.0956040927571</v>
+        <v>-921.8135992908541</v>
       </c>
       <c r="J8" t="n">
-        <v>350.17242888629</v>
+        <v>397.0416940626303</v>
       </c>
       <c r="K8" t="n">
-        <v>122620.7299521239</v>
+        <v>157642.1068241233</v>
       </c>
       <c r="L8" t="n">
-        <v>-3858.718602008862</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>-8293.753182469702</v>
+      </c>
+      <c r="M8" t="n">
+        <v>248.6179962158203</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1602.171272316957</v>
+      </c>
       <c r="O8" t="n">
         <v>11</v>
       </c>
       <c r="P8" t="n">
-        <v>49802</v>
+        <v>449</v>
       </c>
       <c r="Q8" t="n">
-        <v>811.8702804</v>
+        <v>258.8843575</v>
       </c>
       <c r="R8" t="n">
-        <v>-413.0663914181831</v>
+        <v>-821.2745780068734</v>
       </c>
       <c r="S8" t="n">
-        <v>-618.8104705500274</v>
+        <v>-861.3116178935904</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8477388530304806</v>
+        <v>0.4834457375098579</v>
       </c>
       <c r="U8" t="n">
-        <v>-620.0050727586137</v>
+        <v>-1055.911225066176</v>
       </c>
       <c r="V8" t="n">
-        <v>-206.1277100777525</v>
+        <v>-586.6379309475702</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>-246.1741128428996</v>
+        <v>-337.2060792199966</v>
       </c>
       <c r="Y8" t="n">
-        <v>-413.0663914181831</v>
+        <v>-821.2745780068734</v>
       </c>
       <c r="Z8" t="n">
-        <v>350.17242888629</v>
+        <v>397.0416940626303</v>
       </c>
       <c r="AA8" t="n">
-        <v>-197.949015942858</v>
+        <v>-287.7574936641852</v>
       </c>
       <c r="AB8" t="n">
         <v>8</v>
@@ -4822,25 +6773,592 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>74.44280014425429</v>
+        <v>110.7684425076133</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8477388530304806</v>
+        <v>0.4834457375098579</v>
       </c>
       <c r="AF8" t="n">
-        <v>54.12020201663768</v>
+        <v>67.41062208845065</v>
       </c>
       <c r="AG8" t="n">
-        <v>-350.7926001826238</v>
+        <v>-753.9775620427001</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>run-20260806_153621-k6y8llea</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>-326.4612258855022</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-205.9221520456136</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1155.798209759019</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-436.9015439899808</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-277.6784635508047</v>
+      </c>
+      <c r="J9" t="n">
+        <v>321.3715533320886</v>
+      </c>
+      <c r="K9" t="n">
+        <v>103279.6752910795</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-8433.802705967337</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.004880172200500965</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.20248047688376</v>
+      </c>
+      <c r="O9" t="n">
+        <v>21</v>
+      </c>
+      <c r="P9" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>498.1407452</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-400.9567107015288</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-433.0586684148304</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.7355697359116188</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-574.3544277959653</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-299.4486601839963</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-253.415954931284</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-436.9015439899808</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>321.3715533320886</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-205.9221520456136</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>37.53842683855429</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.7355697359116188</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>57.61796713254762</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-401.6096526651113</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>run-20260729_141719-t7p5us0r</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>-245.9180673140198</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-219.4573177568721</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1162.450953943689</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-539.6959803689576</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-402.8396155024116</v>
+      </c>
+      <c r="J10" t="n">
+        <v>351.3321372812916</v>
+      </c>
+      <c r="K10" t="n">
+        <v>123434.2706866403</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-5232.471273429679</v>
+      </c>
+      <c r="M10" t="n">
+        <v>74.09199523925781</v>
+      </c>
+      <c r="N10" t="n">
+        <v>192.5587954423366</v>
+      </c>
+      <c r="O10" t="n">
+        <v>11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>199.1797317</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-539.6959803689576</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-697.6821874504836</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6509815712192389</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-747.3200055748785</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-332.0719551630368</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-266.6069995662129</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-539.6959803689576</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>351.3321372812916</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-219.4573177568721</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>80.7308572839803</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.6509815712192389</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>60.5700280022815</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-475.6792066754253</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>run-20260806_152834-xy4luccb</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>-311.4664162905647</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-197.9138957092919</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1155.798209759019</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-347.0494662007257</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-276.0082766384609</v>
+      </c>
+      <c r="J11" t="n">
+        <v>240.2571253039864</v>
+      </c>
+      <c r="K11" t="n">
+        <v>57723.48625933543</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-6554.406477190447</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01735409535467625</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.645528168181698</v>
+      </c>
+      <c r="O11" t="n">
+        <v>21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>427.8886858</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-306.6120290228109</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-397.9564814102443</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.692284958493574</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-449.8091360768065</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-244.289796324645</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-245.8081114117782</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-347.0494662007257</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>240.2571253039864</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-197.9138957092919</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>21.07368615209907</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.692284958493574</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>59.09170290623943</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-312.114594151926</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>run-20260729_113328-cyshpsut</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>-218.3302575957343</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-195.508550465746</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1155.753749675708</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-341.7296554947541</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-267.158253364485</v>
+      </c>
+      <c r="J12" t="n">
+        <v>274.3809319585858</v>
+      </c>
+      <c r="K12" t="n">
+        <v>75284.8958224621</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-3071.984206806574</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>49901</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1098.9359443</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-341.7296554947541</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-586.9318502204624</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.8029181183041865</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-503.8784243885669</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-179.5808866009412</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-243.5208104262441</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-341.7296554947541</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>274.3809319585858</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-195.508550465746</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>44.99462884190318</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.8029181183041865</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>55.46563595137608</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-279.2712915278703</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TD3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pendulum-v1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>run-20260729_111932-9hz3to4q</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>-207.5724532386165</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-197.949015942858</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1162.450953943689</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-413.0663914181831</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-263.0956040927571</v>
+      </c>
+      <c r="J13" t="n">
+        <v>350.17242888629</v>
+      </c>
+      <c r="K13" t="n">
+        <v>122620.7299521239</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-3858.718602008862</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>11</v>
+      </c>
+      <c r="P13" t="n">
+        <v>49802</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>811.8702804</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-413.0663914181831</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-618.8104705500274</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.8477388530304806</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-620.0050727586137</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-206.1277100777525</v>
+      </c>
+      <c r="W13" t="n">
+        <v>5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-246.1741128428996</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-413.0663914181831</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>350.17242888629</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-197.949015942858</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>74.44280014425429</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.8477388530304806</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>54.12020201663768</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-350.7926001826238</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4853,7 +7371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5159,7 +7677,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5172,7 +7690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>run-20260729_204909-pgay1oio</t>
+          <t>run-20260806_160343-r2g5psh1</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -5197,22 +7715,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006548303179442883</v>
+        <v>0.150246262550354</v>
       </c>
       <c r="N3" t="n">
-        <v>71.73304060848238</v>
+        <v>1606.367472619675</v>
       </c>
       <c r="O3" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="P3" t="n">
-        <v>449</v>
+        <v>1241</v>
       </c>
       <c r="Q3" t="n">
-        <v>182.1001624</v>
+        <v>880.1615329</v>
       </c>
       <c r="R3" t="n">
         <v>-200</v>
@@ -5251,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.840691781539163e-16</v>
+        <v>-3.555082100765894e-16</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -5260,7 +7778,7 @@
         <v>100</v>
       </c>
       <c r="AG3" t="n">
-        <v>-181.8181818181818</v>
+        <v>-195.1219512195122</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="b">
@@ -5268,6 +7786,232 @@
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MountainCar-v0</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>run-20260729_204909-pgay1oio</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.006548303179442883</v>
+      </c>
+      <c r="N4" t="n">
+        <v>71.73304060848238</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11</v>
+      </c>
+      <c r="P4" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>182.1001624</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.840691781539163e-16</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-181.8181818181818</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MountainCar-v0</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>run-20260806_155127-hzh7i4t3</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.002150806365534663</v>
+      </c>
+      <c r="N5" t="n">
+        <v>64.25386444770818</v>
+      </c>
+      <c r="O5" t="n">
+        <v>41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1241</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>599.8824757</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-3.555082100765894e-16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-195.1219512195122</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
